--- a/artfynd/A 3370-2022 artfynd.xlsx
+++ b/artfynd/A 3370-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3370-2022 artfynd.xlsx
+++ b/artfynd/A 3370-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110941115</v>
+        <v>110941064</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551354.824395216</v>
+        <v>551402</v>
       </c>
       <c r="R2" t="n">
-        <v>7261155.82732508</v>
+        <v>7261213</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110940996</v>
+        <v>110941007</v>
       </c>
       <c r="B3" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551373.5405760778</v>
+        <v>551304</v>
       </c>
       <c r="R3" t="n">
-        <v>7261203.970236649</v>
+        <v>7261170</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110941068</v>
+        <v>110941062</v>
       </c>
       <c r="B4" t="n">
-        <v>95532</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551355.963019617</v>
+        <v>551296</v>
       </c>
       <c r="R4" t="n">
-        <v>7261162.083940708</v>
+        <v>7261079</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110941104</v>
+        <v>110941115</v>
       </c>
       <c r="B5" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551401.1569131658</v>
+        <v>551355</v>
       </c>
       <c r="R5" t="n">
-        <v>7261219.424205756</v>
+        <v>7261156</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110940993</v>
+        <v>110940987</v>
       </c>
       <c r="B6" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551318.9644424435</v>
+        <v>551305</v>
       </c>
       <c r="R6" t="n">
-        <v>7261159.354003564</v>
+        <v>7261169</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,50 +1210,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110940961</v>
+        <v>110940996</v>
       </c>
       <c r="B7" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551432.189812852</v>
+        <v>551373</v>
       </c>
       <c r="R7" t="n">
-        <v>7261229.949462338</v>
+        <v>7261204</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,15 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110940987</v>
+        <v>110941068</v>
       </c>
       <c r="B8" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551305.0568704712</v>
+        <v>551356</v>
       </c>
       <c r="R8" t="n">
-        <v>7261169.087877396</v>
+        <v>7261162</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,37 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110941064</v>
+        <v>110940993</v>
       </c>
       <c r="B9" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551402.0916758431</v>
+        <v>551319</v>
       </c>
       <c r="R9" t="n">
-        <v>7261213.619986809</v>
+        <v>7261159</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,37 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110941007</v>
+        <v>110941116</v>
       </c>
       <c r="B10" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551303.7865699112</v>
+        <v>551459</v>
       </c>
       <c r="R10" t="n">
-        <v>7261170.312846533</v>
+        <v>7261273</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,59 +1643,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110940978</v>
+        <v>110941117</v>
       </c>
       <c r="B11" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551435.8453106785</v>
+        <v>551466</v>
       </c>
       <c r="R11" t="n">
-        <v>7261258.701336128</v>
+        <v>7261282</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,6 +1747,229 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110940961</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>551432</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7261230</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110940978</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>551436</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7261259</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
